--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/19.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/19.xlsx
@@ -426,13 +426,13 @@
         <v>-9.779177626214883</v>
       </c>
       <c r="E2">
-        <v>-5.715638187858782</v>
+        <v>-7.706790095135408</v>
       </c>
       <c r="F2">
-        <v>-4.320424061247178</v>
+        <v>-4.057294812482721</v>
       </c>
       <c r="G2">
-        <v>-9.325847661341738</v>
+        <v>-8.653912854326945</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.56534952241661</v>
       </c>
       <c r="E3">
-        <v>-6.364668139586113</v>
+        <v>-8.203273871440354</v>
       </c>
       <c r="F3">
-        <v>-4.20361597377842</v>
+        <v>-4.159858294092939</v>
       </c>
       <c r="G3">
-        <v>-9.488786091693589</v>
+        <v>-8.502746723912743</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.5140855094893</v>
       </c>
       <c r="E4">
-        <v>-7.576723264687099</v>
+        <v>-8.275738512511095</v>
       </c>
       <c r="F4">
-        <v>-4.298707581415386</v>
+        <v>-3.831633449714288</v>
       </c>
       <c r="G4">
-        <v>-8.556811243114582</v>
+        <v>-8.307530474553001</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.49332878051479</v>
       </c>
       <c r="E5">
-        <v>-7.019385854667078</v>
+        <v>-8.88085132331204</v>
       </c>
       <c r="F5">
-        <v>-4.268318094876284</v>
+        <v>-3.828223061116963</v>
       </c>
       <c r="G5">
-        <v>-8.49490404153021</v>
+        <v>-7.753100170909097</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.48694775763762</v>
       </c>
       <c r="E6">
-        <v>-7.781315191879639</v>
+        <v>-9.807752968624031</v>
       </c>
       <c r="F6">
-        <v>-4.305190384709696</v>
+        <v>-3.76501862828336</v>
       </c>
       <c r="G6">
-        <v>-8.895880627792275</v>
+        <v>-7.891656433364215</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.44658991561104</v>
       </c>
       <c r="E7">
-        <v>-9.430001252326193</v>
+        <v>-10.51174500938246</v>
       </c>
       <c r="F7">
-        <v>-4.217446395935561</v>
+        <v>-3.603062860627223</v>
       </c>
       <c r="G7">
-        <v>-7.579087965728387</v>
+        <v>-8.338444348798715</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.3414247893245</v>
       </c>
       <c r="E8">
-        <v>-9.266500698279255</v>
+        <v>-10.87746909871592</v>
       </c>
       <c r="F8">
-        <v>-4.028230713788098</v>
+        <v>-3.70190945770108</v>
       </c>
       <c r="G8">
-        <v>-8.12860873033755</v>
+        <v>-7.639737160007835</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.1231311540268</v>
       </c>
       <c r="E9">
-        <v>-9.645633599149432</v>
+        <v>-11.45791078312308</v>
       </c>
       <c r="F9">
-        <v>-3.964294832537823</v>
+        <v>-3.344699209531071</v>
       </c>
       <c r="G9">
-        <v>-7.406356941671373</v>
+        <v>-8.054819980812734</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.74933690257914</v>
       </c>
       <c r="E10">
-        <v>-10.58832603332617</v>
+        <v>-12.17177036874422</v>
       </c>
       <c r="F10">
-        <v>-3.870886467463345</v>
+        <v>-3.507809721346711</v>
       </c>
       <c r="G10">
-        <v>-6.915512286200252</v>
+        <v>-7.797428375679939</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.17147864552824</v>
       </c>
       <c r="E11">
-        <v>-12.41689213830541</v>
+        <v>-12.41979489014432</v>
       </c>
       <c r="F11">
-        <v>-4.043278836027353</v>
+        <v>-3.216107595757491</v>
       </c>
       <c r="G11">
-        <v>-7.191429704170809</v>
+        <v>-7.952517502558176</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.34890446412449</v>
       </c>
       <c r="E12">
-        <v>-11.87034608184566</v>
+        <v>-13.13259481284767</v>
       </c>
       <c r="F12">
-        <v>-3.503667055965311</v>
+        <v>-3.043655584740481</v>
       </c>
       <c r="G12">
-        <v>-6.874749538975205</v>
+        <v>-7.17770418236499</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.24262542064272</v>
       </c>
       <c r="E13">
-        <v>-12.18767436945916</v>
+        <v>-13.6727013792685</v>
       </c>
       <c r="F13">
-        <v>-3.188051620192074</v>
+        <v>-2.940316751241243</v>
       </c>
       <c r="G13">
-        <v>-6.291785643328325</v>
+        <v>-6.540801568246764</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.83361332052237</v>
       </c>
       <c r="E14">
-        <v>-14.04427172854587</v>
+        <v>-14.3882455572205</v>
       </c>
       <c r="F14">
-        <v>-3.201433067216897</v>
+        <v>-2.296555994360023</v>
       </c>
       <c r="G14">
-        <v>-5.923603321178279</v>
+        <v>-6.543446694132641</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.11493689106658</v>
       </c>
       <c r="E15">
-        <v>-13.27739276924293</v>
+        <v>-14.17015424901109</v>
       </c>
       <c r="F15">
-        <v>-2.939393121587121</v>
+        <v>-2.250410131452271</v>
       </c>
       <c r="G15">
-        <v>-5.744668334780672</v>
+        <v>-6.618625872783951</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.10034188199114</v>
       </c>
       <c r="E16">
-        <v>-15.32155499325334</v>
+        <v>-15.6674353094852</v>
       </c>
       <c r="F16">
-        <v>-2.560344623577109</v>
+        <v>-1.924681158058255</v>
       </c>
       <c r="G16">
-        <v>-4.825756898899629</v>
+        <v>-6.082079136143191</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.82340837693557</v>
       </c>
       <c r="E17">
-        <v>-14.37654850885869</v>
+        <v>-16.34140356757277</v>
       </c>
       <c r="F17">
-        <v>-2.590072244561375</v>
+        <v>-2.01676579202306</v>
       </c>
       <c r="G17">
-        <v>-4.193293726349565</v>
+        <v>-5.019672103862439</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.34421261420084</v>
       </c>
       <c r="E18">
-        <v>-15.27274710039867</v>
+        <v>-17.18993091323401</v>
       </c>
       <c r="F18">
-        <v>-1.965257078549584</v>
+        <v>-1.502477203464598</v>
       </c>
       <c r="G18">
-        <v>-4.144814097472478</v>
+        <v>-5.120296135528586</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.74211904881154</v>
       </c>
       <c r="E19">
-        <v>-16.22750791780585</v>
+        <v>-17.09117848054874</v>
       </c>
       <c r="F19">
-        <v>-1.644997815116253</v>
+        <v>-1.176932127634003</v>
       </c>
       <c r="G19">
-        <v>-3.821075849187149</v>
+        <v>-4.511159066848228</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.104310524420816</v>
       </c>
       <c r="E20">
-        <v>-17.73190321094601</v>
+        <v>-19.12206321876867</v>
       </c>
       <c r="F20">
-        <v>-1.766940952114965</v>
+        <v>-0.9919146114839281</v>
       </c>
       <c r="G20">
-        <v>-4.474213378629961</v>
+        <v>-5.144148616139035</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.51861950375398</v>
       </c>
       <c r="E21">
-        <v>-18.4991625620656</v>
+        <v>-19.51100932281347</v>
       </c>
       <c r="F21">
-        <v>-1.250028923991837</v>
+        <v>-0.5848631534222791</v>
       </c>
       <c r="G21">
-        <v>-4.585192796742949</v>
+        <v>-4.633314886701795</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.064775096276955</v>
       </c>
       <c r="E22">
-        <v>-18.47998900311712</v>
+        <v>-20.15842260932006</v>
       </c>
       <c r="F22">
-        <v>-1.136667673286128</v>
+        <v>-0.04224771315768534</v>
       </c>
       <c r="G22">
-        <v>-3.882082582384838</v>
+        <v>-4.608247435878433</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.818113934104909</v>
       </c>
       <c r="E23">
-        <v>-18.9606095349732</v>
+        <v>-20.46846458225521</v>
       </c>
       <c r="F23">
-        <v>-1.332246045454494</v>
+        <v>-0.3707616577599133</v>
       </c>
       <c r="G23">
-        <v>-3.477384942936632</v>
+        <v>-4.930704503040065</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.835834091965965</v>
       </c>
       <c r="E24">
-        <v>-19.21086206558508</v>
+        <v>-21.17842062328174</v>
       </c>
       <c r="F24">
-        <v>-0.6619385984157591</v>
+        <v>0.2484926778768851</v>
       </c>
       <c r="G24">
-        <v>-4.887207245199581</v>
+        <v>-4.431470925172431</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.160415573695684</v>
       </c>
       <c r="E25">
-        <v>-19.09915366876386</v>
+        <v>-21.13558578764318</v>
       </c>
       <c r="F25">
-        <v>-0.9260718284724094</v>
+        <v>-0.03043022378934759</v>
       </c>
       <c r="G25">
-        <v>-4.402050106964928</v>
+        <v>-5.348273543544957</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.809754638687803</v>
       </c>
       <c r="E26">
-        <v>-19.86613678296898</v>
+        <v>-20.78014586278114</v>
       </c>
       <c r="F26">
-        <v>-0.9493075341209356</v>
+        <v>-0.1248674211781024</v>
       </c>
       <c r="G26">
-        <v>-3.810680736193837</v>
+        <v>-5.124748819278906</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.78378976875361</v>
       </c>
       <c r="E27">
-        <v>-20.24187785680742</v>
+        <v>-21.09985612772267</v>
       </c>
       <c r="F27">
-        <v>-0.6391891444326763</v>
+        <v>-0.09890721514176873</v>
       </c>
       <c r="G27">
-        <v>-5.312052864799791</v>
+        <v>-5.632583194457567</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.052832616933389</v>
       </c>
       <c r="E28">
-        <v>-20.14436622600025</v>
+        <v>-21.84941367394627</v>
       </c>
       <c r="F28">
-        <v>-0.471739644161173</v>
+        <v>-0.1304290799204983</v>
       </c>
       <c r="G28">
-        <v>-5.736252928019844</v>
+        <v>-5.18414662734451</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.568725909622323</v>
       </c>
       <c r="E29">
-        <v>-20.72885636617027</v>
+        <v>-21.25061355591202</v>
       </c>
       <c r="F29">
-        <v>-0.4595717553814511</v>
+        <v>-0.1166442179705117</v>
       </c>
       <c r="G29">
-        <v>-4.686445832061558</v>
+        <v>-5.502343022397099</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.267185859020587</v>
       </c>
       <c r="E30">
-        <v>-20.54460181574617</v>
+        <v>-21.95119565574267</v>
       </c>
       <c r="F30">
-        <v>-0.9091292299829512</v>
+        <v>-0.1732805256673167</v>
       </c>
       <c r="G30">
-        <v>-5.417063369305474</v>
+        <v>-5.770450863440516</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.082497412842348</v>
       </c>
       <c r="E31">
-        <v>-19.11542447587343</v>
+        <v>-21.05798132857374</v>
       </c>
       <c r="F31">
-        <v>-0.8619835276200201</v>
+        <v>-0.4647399396075172</v>
       </c>
       <c r="G31">
-        <v>-4.823290542472872</v>
+        <v>-5.151511269418375</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.953552266770028</v>
       </c>
       <c r="E32">
-        <v>-20.32112615194165</v>
+        <v>-21.49375185385785</v>
       </c>
       <c r="F32">
-        <v>-1.163833982260938</v>
+        <v>-0.7115039619622675</v>
       </c>
       <c r="G32">
-        <v>-4.889713328172809</v>
+        <v>-4.772155856073289</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.829999555010293</v>
       </c>
       <c r="E33">
-        <v>-19.55141689638391</v>
+        <v>-20.15769352500482</v>
       </c>
       <c r="F33">
-        <v>-1.051208321808914</v>
+        <v>-0.6704384763358848</v>
       </c>
       <c r="G33">
-        <v>-4.957658964820811</v>
+        <v>-4.860507695425358</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.677051149197324</v>
       </c>
       <c r="E34">
-        <v>-17.99043832051791</v>
+        <v>-19.8706924278207</v>
       </c>
       <c r="F34">
-        <v>-1.201288614378517</v>
+        <v>-0.5497503159524136</v>
       </c>
       <c r="G34">
-        <v>-4.540371320686757</v>
+        <v>-4.82547881307433</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.468059751046766</v>
       </c>
       <c r="E35">
-        <v>-18.62184345140739</v>
+        <v>-19.74193432636061</v>
       </c>
       <c r="F35">
-        <v>-0.6711931190398351</v>
+        <v>-0.4790905764936158</v>
       </c>
       <c r="G35">
-        <v>-5.863162691267806</v>
+        <v>-4.832176046700276</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.183837263952686</v>
       </c>
       <c r="E36">
-        <v>-18.94268130637683</v>
+        <v>-19.79164791401681</v>
       </c>
       <c r="F36">
-        <v>-0.4562027851542655</v>
+        <v>-0.6929742115290454</v>
       </c>
       <c r="G36">
-        <v>-4.45568425524666</v>
+        <v>-4.51023542464277</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.808304372467912</v>
       </c>
       <c r="E37">
-        <v>-18.30390834827687</v>
+        <v>-19.79393479339069</v>
       </c>
       <c r="F37">
-        <v>-1.03615191589563</v>
+        <v>-0.5944564763141001</v>
       </c>
       <c r="G37">
-        <v>-4.976343683844457</v>
+        <v>-4.406704733993143</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.33454027702456</v>
       </c>
       <c r="E38">
-        <v>-17.74340100645148</v>
+        <v>-19.36209498354523</v>
       </c>
       <c r="F38">
-        <v>-0.5117158266528743</v>
+        <v>-0.5166031943293914</v>
       </c>
       <c r="G38">
-        <v>-4.293666156554728</v>
+        <v>-4.405334168139885</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.75507128879043</v>
       </c>
       <c r="E39">
-        <v>-16.97676205627094</v>
+        <v>-19.01549916842017</v>
       </c>
       <c r="F39">
-        <v>-0.6072688349332002</v>
+        <v>-0.6112184907097482</v>
       </c>
       <c r="G39">
-        <v>-4.661729299065359</v>
+        <v>-3.676838690586642</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.06509484115372</v>
       </c>
       <c r="E40">
-        <v>-17.44596630515369</v>
+        <v>-17.74439274225916</v>
       </c>
       <c r="F40">
-        <v>-1.04904711125501</v>
+        <v>-0.8488273965287584</v>
       </c>
       <c r="G40">
-        <v>-3.690782708398052</v>
+        <v>-3.881824359832775</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.26126256028476</v>
       </c>
       <c r="E41">
-        <v>-16.32829816379457</v>
+        <v>-18.04673178090727</v>
       </c>
       <c r="F41">
-        <v>-0.7595517564268472</v>
+        <v>-0.6297109646098443</v>
       </c>
       <c r="G41">
-        <v>-3.317293581748556</v>
+        <v>-3.508937752471426</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.34242186246326</v>
       </c>
       <c r="E42">
-        <v>-15.38898397122755</v>
+        <v>-18.01630949252374</v>
       </c>
       <c r="F42">
-        <v>-1.248061551410188</v>
+        <v>-0.9876568030335388</v>
       </c>
       <c r="G42">
-        <v>-3.934025041896003</v>
+        <v>-3.662060415299336</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.30290923437635</v>
       </c>
       <c r="E43">
-        <v>-15.63382044692626</v>
+        <v>-17.28729763287293</v>
       </c>
       <c r="F43">
-        <v>-1.058221280241015</v>
+        <v>-0.7874718797382045</v>
       </c>
       <c r="G43">
-        <v>-4.268486147183031</v>
+        <v>-3.345946353390948</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.1345748066567</v>
       </c>
       <c r="E44">
-        <v>-16.07219484476478</v>
+        <v>-16.63113986305753</v>
       </c>
       <c r="F44">
-        <v>-1.086684812568608</v>
+        <v>-0.9708533702677508</v>
       </c>
       <c r="G44">
-        <v>-3.62965348501541</v>
+        <v>-3.441650914385738</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.83626964017049</v>
       </c>
       <c r="E45">
-        <v>-14.56350655826536</v>
+        <v>-16.08711163814605</v>
       </c>
       <c r="F45">
-        <v>-1.424324880847478</v>
+        <v>-1.061461025153363</v>
       </c>
       <c r="G45">
-        <v>-3.085946038373207</v>
+        <v>-3.06512601747673</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.4140926621447</v>
       </c>
       <c r="E46">
-        <v>-15.38567365672795</v>
+        <v>-16.28488821195704</v>
       </c>
       <c r="F46">
-        <v>-1.188004914707224</v>
+        <v>-0.9591096055982621</v>
       </c>
       <c r="G46">
-        <v>-3.732611451286744</v>
+        <v>-3.123626667701191</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.884391102697709</v>
       </c>
       <c r="E47">
-        <v>-13.88454339334733</v>
+        <v>-15.88395070873993</v>
       </c>
       <c r="F47">
-        <v>-1.605434159591146</v>
+        <v>-1.3195836213353</v>
       </c>
       <c r="G47">
-        <v>-3.545731155594885</v>
+        <v>-3.2208838745539</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.266939423885983</v>
       </c>
       <c r="E48">
-        <v>-13.81349616464098</v>
+        <v>-15.10724496084034</v>
       </c>
       <c r="F48">
-        <v>-1.365998703648962</v>
+        <v>-1.517205575886373</v>
       </c>
       <c r="G48">
-        <v>-3.639085229256794</v>
+        <v>-2.996759941545241</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.59034656306255</v>
       </c>
       <c r="E49">
-        <v>-13.21646667994373</v>
+        <v>-15.25220141382587</v>
       </c>
       <c r="F49">
-        <v>-1.629791474703062</v>
+        <v>-1.399444865904395</v>
       </c>
       <c r="G49">
-        <v>-3.397842465264563</v>
+        <v>-3.635811099718454</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.8835616731826</v>
       </c>
       <c r="E50">
-        <v>-12.58003041443173</v>
+        <v>-14.71140199088186</v>
       </c>
       <c r="F50">
-        <v>-1.741755269600249</v>
+        <v>-1.531998560965567</v>
       </c>
       <c r="G50">
-        <v>-4.100475961065019</v>
+        <v>-3.065933790588312</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.178633475081945</v>
       </c>
       <c r="E51">
-        <v>-12.88669414575716</v>
+        <v>-14.69603235009983</v>
       </c>
       <c r="F51">
-        <v>-1.962420748562398</v>
+        <v>-1.778788262709804</v>
       </c>
       <c r="G51">
-        <v>-3.420215132018958</v>
+        <v>-3.000063865993433</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.504314006451549</v>
       </c>
       <c r="E52">
-        <v>-12.93051166025538</v>
+        <v>-13.95192255810745</v>
       </c>
       <c r="F52">
-        <v>-1.865736190409848</v>
+        <v>-1.572929851072696</v>
       </c>
       <c r="G52">
-        <v>-3.048712332693023</v>
+        <v>-2.84422986636886</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.886411761975502</v>
       </c>
       <c r="E53">
-        <v>-12.69504459727854</v>
+        <v>-13.32503684427763</v>
       </c>
       <c r="F53">
-        <v>-2.03471817037653</v>
+        <v>-1.510856968111318</v>
       </c>
       <c r="G53">
-        <v>-3.202963891549825</v>
+        <v>-3.12213361166298</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.349098407557023</v>
       </c>
       <c r="E54">
-        <v>-12.60605102607981</v>
+        <v>-13.42092275291604</v>
       </c>
       <c r="F54">
-        <v>-1.814263925102095</v>
+        <v>-1.851096453300173</v>
       </c>
       <c r="G54">
-        <v>-2.612898875721207</v>
+        <v>-3.306958058574951</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.913738079269501</v>
       </c>
       <c r="E55">
-        <v>-11.06755179518789</v>
+        <v>-12.67232977165607</v>
       </c>
       <c r="F55">
-        <v>-2.078657262523225</v>
+        <v>-1.741263219362986</v>
       </c>
       <c r="G55">
-        <v>-4.07871574523539</v>
+        <v>-3.233808244339215</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.597556674458422</v>
       </c>
       <c r="E56">
-        <v>-11.68554358606665</v>
+        <v>-12.97058865522326</v>
       </c>
       <c r="F56">
-        <v>-1.983664230607191</v>
+        <v>-2.339282356629019</v>
       </c>
       <c r="G56">
-        <v>-4.484002661789586</v>
+        <v>-3.434510067657531</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.408794676817299</v>
       </c>
       <c r="E57">
-        <v>-10.52317487777782</v>
+        <v>-12.78748886567113</v>
       </c>
       <c r="F57">
-        <v>-2.261742197522569</v>
+        <v>-1.828004055212331</v>
       </c>
       <c r="G57">
-        <v>-4.155897803937957</v>
+        <v>-3.43301370107378</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.356505125950713</v>
       </c>
       <c r="E58">
-        <v>-9.953642287255139</v>
+        <v>-13.35014723265016</v>
       </c>
       <c r="F58">
-        <v>-1.908130377350321</v>
+        <v>-1.991511355013911</v>
       </c>
       <c r="G58">
-        <v>-4.021721393231297</v>
+        <v>-3.593058714624306</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.442979220580401</v>
       </c>
       <c r="E59">
-        <v>-10.09799645319765</v>
+        <v>-12.54787824897727</v>
       </c>
       <c r="F59">
-        <v>-1.788737783584829</v>
+        <v>-2.085314851339525</v>
       </c>
       <c r="G59">
-        <v>-4.177538840128173</v>
+        <v>-3.755417799506783</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.671861366722672</v>
       </c>
       <c r="E60">
-        <v>-9.244003239409148</v>
+        <v>-11.46816324827645</v>
       </c>
       <c r="F60">
-        <v>-2.208825259464334</v>
+        <v>-2.272595467234048</v>
       </c>
       <c r="G60">
-        <v>-3.799345428267372</v>
+        <v>-4.112423719916249</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.038327850584576</v>
       </c>
       <c r="E61">
-        <v>-9.344286296309008</v>
+        <v>-11.32669824875083</v>
       </c>
       <c r="F61">
-        <v>-2.431996549819951</v>
+        <v>-2.370642689764203</v>
       </c>
       <c r="G61">
-        <v>-4.523176347155782</v>
+        <v>-4.174188568042431</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.535286476090476</v>
       </c>
       <c r="E62">
-        <v>-9.259286839185036</v>
+        <v>-11.17470454715738</v>
       </c>
       <c r="F62">
-        <v>-2.162314914899349</v>
+        <v>-2.311146029425531</v>
       </c>
       <c r="G62">
-        <v>-3.921259578296573</v>
+        <v>-4.316849906966245</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.147878667157518</v>
       </c>
       <c r="E63">
-        <v>-10.42539153853019</v>
+        <v>-11.19203048871073</v>
       </c>
       <c r="F63">
-        <v>-2.434800573478427</v>
+        <v>-2.209954324234349</v>
       </c>
       <c r="G63">
-        <v>-5.050000011547702</v>
+        <v>-4.43710547368027</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.859844011644562</v>
       </c>
       <c r="E64">
-        <v>-9.46289608751791</v>
+        <v>-10.63188542480595</v>
       </c>
       <c r="F64">
-        <v>-2.405425837007754</v>
+        <v>-2.398939720243834</v>
       </c>
       <c r="G64">
-        <v>-4.450215234015785</v>
+        <v>-4.373033175313216</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.649635280638831</v>
       </c>
       <c r="E65">
-        <v>-8.464136616652207</v>
+        <v>-10.46465340817669</v>
       </c>
       <c r="F65">
-        <v>-2.747633523145661</v>
+        <v>-2.296845922951003</v>
       </c>
       <c r="G65">
-        <v>-4.351504697671335</v>
+        <v>-4.804393948534712</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.493389847498806</v>
       </c>
       <c r="E66">
-        <v>-9.025739849187453</v>
+        <v>-11.06647401837406</v>
       </c>
       <c r="F66">
-        <v>-2.430962747301257</v>
+        <v>-2.621221344008845</v>
       </c>
       <c r="G66">
-        <v>-4.732025423046244</v>
+        <v>-4.593604892958237</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.36876407562101</v>
       </c>
       <c r="E67">
-        <v>-7.8320069299215</v>
+        <v>-10.81486747403389</v>
       </c>
       <c r="F67">
-        <v>-2.57626998689593</v>
+        <v>-2.416741335729995</v>
       </c>
       <c r="G67">
-        <v>-4.986603064470659</v>
+        <v>-4.44950677727038</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.25322188039856</v>
       </c>
       <c r="E68">
-        <v>-8.811973233655374</v>
+        <v>-10.39413148245524</v>
       </c>
       <c r="F68">
-        <v>-2.587057815582588</v>
+        <v>-2.239406098873483</v>
       </c>
       <c r="G68">
-        <v>-4.948230531124967</v>
+        <v>-4.679103042055455</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.12459673331124</v>
       </c>
       <c r="E69">
-        <v>-7.82522327585801</v>
+        <v>-10.02946252756557</v>
       </c>
       <c r="F69">
-        <v>-2.447333772282784</v>
+        <v>-2.817732457872763</v>
       </c>
       <c r="G69">
-        <v>-4.683310745435868</v>
+        <v>-4.697102478152472</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.95658001456709</v>
       </c>
       <c r="E70">
-        <v>-8.362753140568481</v>
+        <v>-9.931113129066979</v>
       </c>
       <c r="F70">
-        <v>-2.642888121796469</v>
+        <v>-2.780421961683271</v>
       </c>
       <c r="G70">
-        <v>-4.539060344653205</v>
+        <v>-5.051608936679788</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.72727591051425</v>
       </c>
       <c r="E71">
-        <v>-8.215328669248773</v>
+        <v>-10.59581612933486</v>
       </c>
       <c r="F71">
-        <v>-2.892242449019773</v>
+        <v>-2.834921081480853</v>
       </c>
       <c r="G71">
-        <v>-4.271339837437884</v>
+        <v>-4.683416682893125</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.41197251277784</v>
       </c>
       <c r="E72">
-        <v>-8.720778824088908</v>
+        <v>-9.291692599183925</v>
       </c>
       <c r="F72">
-        <v>-2.876746180015603</v>
+        <v>-2.867879335336037</v>
       </c>
       <c r="G72">
-        <v>-4.254704346103046</v>
+        <v>-4.159797626583219</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.99502959540279</v>
       </c>
       <c r="E73">
-        <v>-8.886108881634945</v>
+        <v>-10.54597574440644</v>
       </c>
       <c r="F73">
-        <v>-2.685199471996662</v>
+        <v>-2.69072633930814</v>
       </c>
       <c r="G73">
-        <v>-4.667310878844571</v>
+        <v>-4.150809495444098</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.46170800361386</v>
       </c>
       <c r="E74">
-        <v>-8.355258516085787</v>
+        <v>-10.23857387181776</v>
       </c>
       <c r="F74">
-        <v>-2.667871682664902</v>
+        <v>-2.773845552872445</v>
       </c>
       <c r="G74">
-        <v>-4.137643455834416</v>
+        <v>-3.639257377624836</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.80632910877568</v>
       </c>
       <c r="E75">
-        <v>-8.57988441228826</v>
+        <v>-10.7662271347175</v>
       </c>
       <c r="F75">
-        <v>-2.947072087411073</v>
+        <v>-2.917054537835827</v>
       </c>
       <c r="G75">
-        <v>-3.665817884486408</v>
+        <v>-4.112562762828898</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.02854363452014</v>
       </c>
       <c r="E76">
-        <v>-9.194457205291227</v>
+        <v>-10.96663928040096</v>
       </c>
       <c r="F76">
-        <v>-3.01938276310365</v>
+        <v>-3.04401343945849</v>
       </c>
       <c r="G76">
-        <v>-3.961913077518823</v>
+        <v>-3.647457598925611</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.1345990791899</v>
       </c>
       <c r="E77">
-        <v>-10.40822409356711</v>
+        <v>-11.17172028278633</v>
       </c>
       <c r="F77">
-        <v>-2.913523207597692</v>
+        <v>-3.023675362984957</v>
       </c>
       <c r="G77">
-        <v>-4.993280434823369</v>
+        <v>-3.814759328298219</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.13802700809157</v>
       </c>
       <c r="E78">
-        <v>-10.14688585858446</v>
+        <v>-11.39716583278419</v>
       </c>
       <c r="F78">
-        <v>-2.91503746321001</v>
+        <v>-3.258063576341883</v>
       </c>
       <c r="G78">
-        <v>-4.666423652640046</v>
+        <v>-3.293868161512673</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.05494674448337</v>
       </c>
       <c r="E79">
-        <v>-10.71800341500982</v>
+        <v>-11.90884263938487</v>
       </c>
       <c r="F79">
-        <v>-3.558881056831509</v>
+        <v>-3.380813543190921</v>
       </c>
       <c r="G79">
-        <v>-4.219645668842164</v>
+        <v>-2.975771082826261</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.90820981300863</v>
       </c>
       <c r="E80">
-        <v>-11.37421099803931</v>
+        <v>-13.01657078029715</v>
       </c>
       <c r="F80">
-        <v>-3.54383790479667</v>
+        <v>-3.104751822533959</v>
       </c>
       <c r="G80">
-        <v>-3.5146848595276</v>
+        <v>-2.989973323189735</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.71568965779049</v>
       </c>
       <c r="E81">
-        <v>-11.50052372353526</v>
+        <v>-13.51300927186202</v>
       </c>
       <c r="F81">
-        <v>-3.201441350890925</v>
+        <v>-3.305233301359495</v>
       </c>
       <c r="G81">
-        <v>-4.30992093515255</v>
+        <v>-3.055429429592205</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.49712410360057</v>
       </c>
       <c r="E82">
-        <v>-12.85813306019078</v>
+        <v>-14.07550461377678</v>
       </c>
       <c r="F82">
-        <v>-3.395410205195652</v>
+        <v>-3.070305820823346</v>
       </c>
       <c r="G82">
-        <v>-3.254571985961524</v>
+        <v>-2.708706063627715</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.26456293103154</v>
       </c>
       <c r="E83">
-        <v>-13.88175838183261</v>
+        <v>-14.4650530048646</v>
       </c>
       <c r="F83">
-        <v>-3.56325483671829</v>
+        <v>-3.699593342442852</v>
       </c>
       <c r="G83">
-        <v>-2.554378362223511</v>
+        <v>-2.772804846359084</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.03452807180776</v>
       </c>
       <c r="E84">
-        <v>-14.2059925923078</v>
+        <v>-14.48983734310858</v>
       </c>
       <c r="F84">
-        <v>-3.308985805694177</v>
+        <v>-3.256309094182753</v>
       </c>
       <c r="G84">
-        <v>-3.205291205063933</v>
+        <v>-2.887237163469532</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.82062151717173</v>
       </c>
       <c r="E85">
-        <v>-14.99097639069341</v>
+        <v>-16.24203979089647</v>
       </c>
       <c r="F85">
-        <v>-3.684550190408014</v>
+        <v>-4.007579514436306</v>
       </c>
       <c r="G85">
-        <v>-3.383368760166869</v>
+        <v>-2.462292227503143</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.63647949076264</v>
       </c>
       <c r="E86">
-        <v>-16.009742659725</v>
+        <v>-17.6537326926256</v>
       </c>
       <c r="F86">
-        <v>-4.130399892514583</v>
+        <v>-3.736623850450199</v>
       </c>
       <c r="G86">
-        <v>-3.429451554073524</v>
+        <v>-2.228928561894378</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.48666038820662</v>
       </c>
       <c r="E87">
-        <v>-17.34004076964027</v>
+        <v>-19.01381457608932</v>
       </c>
       <c r="F87">
-        <v>-4.085084053744436</v>
+        <v>-3.877636833428759</v>
       </c>
       <c r="G87">
-        <v>-3.837661682338897</v>
+        <v>-3.137547511693827</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.36998877920535</v>
       </c>
       <c r="E88">
-        <v>-19.12195453539248</v>
+        <v>-18.82683841278661</v>
       </c>
       <c r="F88">
-        <v>-3.883523212193052</v>
+        <v>-4.081266936752336</v>
       </c>
       <c r="G88">
-        <v>-3.011577943379018</v>
+        <v>-2.954663044467869</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.28698671253517</v>
       </c>
       <c r="E89">
-        <v>-19.78589675202707</v>
+        <v>-21.12887911763783</v>
       </c>
       <c r="F89">
-        <v>-4.26802402444829</v>
+        <v>-4.124742143153463</v>
       </c>
       <c r="G89">
-        <v>-3.521991233532772</v>
+        <v>-2.726390997898502</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.23931851000418</v>
       </c>
       <c r="E90">
-        <v>-21.15995803475247</v>
+        <v>-22.19613175786954</v>
       </c>
       <c r="F90">
-        <v>-4.056449877731866</v>
+        <v>-4.274109211389256</v>
       </c>
       <c r="G90">
-        <v>-2.981508258245818</v>
+        <v>-2.037585650815582</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.23478014907755</v>
       </c>
       <c r="E91">
-        <v>-23.48326898201771</v>
+        <v>-23.49350786174905</v>
       </c>
       <c r="F91">
-        <v>-4.031721454023494</v>
+        <v>-3.936949596204009</v>
       </c>
       <c r="G91">
-        <v>-2.735147390849875</v>
+        <v>-2.912218540108872</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.27646778187972</v>
       </c>
       <c r="E92">
-        <v>-25.74109819513203</v>
+        <v>-26.46886472443073</v>
       </c>
       <c r="F92">
-        <v>-4.557509438867619</v>
+        <v>-4.08425071613722</v>
       </c>
       <c r="G92">
-        <v>-3.708672896492274</v>
+        <v>-3.253025961194684</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.37664174496172</v>
       </c>
       <c r="E93">
-        <v>-28.14941765646926</v>
+        <v>-27.84826507801116</v>
       </c>
       <c r="F93">
-        <v>-4.434892839170431</v>
+        <v>-4.51107447573629</v>
       </c>
       <c r="G93">
-        <v>-3.368507721241081</v>
+        <v>-3.212203624149931</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.54215237983889</v>
       </c>
       <c r="E94">
-        <v>-29.00088851023548</v>
+        <v>-29.96188956482523</v>
       </c>
       <c r="F94">
-        <v>-4.576773951187125</v>
+        <v>-4.338333364495703</v>
       </c>
       <c r="G94">
-        <v>-3.975290992043018</v>
+        <v>-3.792144991719458</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.78674958385758</v>
       </c>
       <c r="E95">
-        <v>-31.63108055557852</v>
+        <v>-32.1091062718282</v>
       </c>
       <c r="F95">
-        <v>-4.016727175665421</v>
+        <v>-4.325810106100181</v>
       </c>
       <c r="G95">
-        <v>-3.548174338202867</v>
+        <v>-3.488607692314761</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.12102151173642</v>
       </c>
       <c r="E96">
-        <v>-35.14061394796799</v>
+        <v>-33.68414575948801</v>
       </c>
       <c r="F96">
-        <v>-4.801463638992074</v>
+        <v>-4.376120171941806</v>
       </c>
       <c r="G96">
-        <v>-3.820165449163849</v>
+        <v>-4.247427767007728</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-14.54014565775524</v>
       </c>
       <c r="E97">
-        <v>-35.77437614957846</v>
+        <v>-36.32370721755292</v>
       </c>
       <c r="F97">
-        <v>-4.523408866363975</v>
+        <v>-4.476657466884777</v>
       </c>
       <c r="G97">
-        <v>-4.032129748406765</v>
+        <v>-4.466188616242768</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.0547890230735</v>
       </c>
       <c r="E98">
-        <v>-39.44069663329849</v>
+        <v>-39.03379965828729</v>
       </c>
       <c r="F98">
-        <v>-4.304111850351251</v>
+        <v>-4.430849577877367</v>
       </c>
       <c r="G98">
-        <v>-5.790516079954038</v>
+        <v>-4.628120640750678</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.63491665063795</v>
       </c>
       <c r="E99">
-        <v>-41.34877821337842</v>
+        <v>-40.83841466423996</v>
       </c>
       <c r="F99">
-        <v>-5.391846057171699</v>
+        <v>-4.493578527821762</v>
       </c>
       <c r="G99">
-        <v>-5.129208124120304</v>
+        <v>-4.991853589695944</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.29964568520161</v>
       </c>
       <c r="E100">
-        <v>-43.75058572909261</v>
+        <v>-43.79016912039366</v>
       </c>
       <c r="F100">
-        <v>-4.665507839007605</v>
+        <v>-4.661486943634416</v>
       </c>
       <c r="G100">
-        <v>-5.102402636888826</v>
+        <v>-5.273922001278466</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.96789180559518</v>
       </c>
       <c r="E101">
-        <v>-45.16946984754593</v>
+        <v>-45.41687849648099</v>
       </c>
       <c r="F101">
-        <v>-4.569481004572878</v>
+        <v>-4.716747333075171</v>
       </c>
       <c r="G101">
-        <v>-5.565809490930468</v>
+        <v>-5.039151353815511</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.71195181237097</v>
       </c>
       <c r="E102">
-        <v>-49.1031967214189</v>
+        <v>-48.3034002845542</v>
       </c>
       <c r="F102">
-        <v>-4.67319094666857</v>
+        <v>-4.402987440284205</v>
       </c>
       <c r="G102">
-        <v>-6.370368062794005</v>
+        <v>-6.179144331354622</v>
       </c>
     </row>
   </sheetData>
